--- a/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w1_0s_h1_0s.xlsx
+++ b/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w1_0s_h1_0s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>sound: engine(96-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
   </si>
   <si>
     <t>sound: engine(0-24), sound: engine(72-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-24), visual: suspicious_near_vehicle(48-144)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1423,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1460,6 +1463,23 @@
         <v>43</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1501,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1545,7 +1565,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1609,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1606,7 +1626,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1650,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1688,13 +1708,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1782,7 +1802,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1826,7 +1846,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
